--- a/outputs/tables/tab-3-coortes-area.xlsx
+++ b/outputs/tables/tab-3-coortes-area.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -523,145 +523,145 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B11">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="C11">
-        <v>1668</v>
+        <v>759</v>
       </c>
       <c r="D11">
-        <v>0.290167865707434</v>
+        <v>0.2661396574440053</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B12">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C12">
-        <v>1666</v>
+        <v>767</v>
       </c>
       <c r="D12">
-        <v>0.2112845138055222</v>
+        <v>0.2633637548891786</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B13">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C13">
-        <v>1655</v>
+        <v>739</v>
       </c>
       <c r="D13">
-        <v>0.113595166163142</v>
+        <v>0.2557510148849797</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B14">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="C14">
-        <v>1656</v>
+        <v>825</v>
       </c>
       <c r="D14">
-        <v>0.02898550724637681</v>
+        <v>0.2339393939393939</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B15">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C15">
-        <v>134</v>
+        <v>799</v>
       </c>
       <c r="D15">
-        <v>0.1567164179104478</v>
+        <v>0.2015018773466833</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B16">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="C16">
-        <v>131</v>
+        <v>807</v>
       </c>
       <c r="D16">
-        <v>0.1984732824427481</v>
+        <v>0.2019826517967782</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B17">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C17">
-        <v>176</v>
+        <v>818</v>
       </c>
       <c r="D17">
-        <v>0.2215909090909091</v>
+        <v>0.2127139364303179</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B18">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C18">
-        <v>180</v>
+        <v>834</v>
       </c>
       <c r="D18">
-        <v>0.2055555555555555</v>
+        <v>0.1858513189448441</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B19">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C19">
-        <v>173</v>
+        <v>794</v>
       </c>
       <c r="D19">
-        <v>0.1907514450867052</v>
+        <v>0.2367758186397985</v>
       </c>
     </row>
     <row r="20">
@@ -671,13 +671,13 @@
         </is>
       </c>
       <c r="B20">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="C20">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D20">
-        <v>0.25</v>
+        <v>0.1567164179104478</v>
       </c>
     </row>
     <row r="21">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="B21">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="C21">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="D21">
-        <v>0.25</v>
+        <v>0.1984732824427481</v>
       </c>
     </row>
     <row r="22">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="B22">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C22">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D22">
-        <v>0.2298850574712644</v>
+        <v>0.2215909090909091</v>
       </c>
     </row>
     <row r="23">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B23">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C23">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D23">
-        <v>0.2265193370165746</v>
+        <v>0.2055555555555555</v>
       </c>
     </row>
     <row r="24">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="B24">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C24">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D24">
-        <v>0.2457142857142857</v>
+        <v>0.1907514450867052</v>
       </c>
     </row>
     <row r="25">
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="B25">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C25">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="D25">
-        <v>0.2378378378378379</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="26">
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="B26">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C26">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D26">
-        <v>0.1186440677966102</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27">
@@ -783,1469 +783,893 @@
         </is>
       </c>
       <c r="B27">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C27">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D27">
-        <v>0.06666666666666667</v>
+        <v>0.2298850574712644</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências Biológicas</t>
         </is>
       </c>
       <c r="B28">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C28">
-        <v>759</v>
+        <v>181</v>
       </c>
       <c r="D28">
-        <v>0.2661396574440053</v>
+        <v>0.2265193370165746</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B29">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C29">
-        <v>767</v>
+        <v>1549</v>
       </c>
       <c r="D29">
-        <v>0.2633637548891786</v>
+        <v>0.1672046481601033</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B30">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C30">
-        <v>739</v>
+        <v>1532</v>
       </c>
       <c r="D30">
-        <v>0.2557510148849797</v>
+        <v>0.1684073107049608</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B31">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C31">
-        <v>825</v>
+        <v>1583</v>
       </c>
       <c r="D31">
-        <v>0.2339393939393939</v>
+        <v>0.1440303221730891</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B32">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C32">
-        <v>799</v>
+        <v>1728</v>
       </c>
       <c r="D32">
-        <v>0.2015018773466833</v>
+        <v>0.1203703703703704</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B33">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C33">
-        <v>807</v>
+        <v>1757</v>
       </c>
       <c r="D33">
-        <v>0.2019826517967782</v>
+        <v>0.1394422310756972</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B34">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C34">
-        <v>818</v>
+        <v>1753</v>
       </c>
       <c r="D34">
-        <v>0.2127139364303179</v>
+        <v>0.1175128351397604</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B35">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C35">
-        <v>834</v>
+        <v>1742</v>
       </c>
       <c r="D35">
-        <v>0.1858513189448441</v>
+        <v>0.1521239954075775</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B36">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C36">
-        <v>794</v>
+        <v>1750</v>
       </c>
       <c r="D36">
-        <v>0.2367758186397985</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B37">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C37">
-        <v>818</v>
+        <v>1754</v>
       </c>
       <c r="D37">
-        <v>0.1907090464547677</v>
+        <v>0.1510832383124287</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B38">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C38">
-        <v>796</v>
+        <v>1996</v>
       </c>
       <c r="D38">
-        <v>0.1909547738693467</v>
+        <v>0.09919839679358718</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B39">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C39">
-        <v>809</v>
+        <v>2026</v>
       </c>
       <c r="D39">
-        <v>0.08034610630407911</v>
+        <v>0.09180651530108588</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B40">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C40">
-        <v>803</v>
+        <v>1955</v>
       </c>
       <c r="D40">
-        <v>0.0199252801992528</v>
+        <v>0.09769820971867008</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B41">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="C41">
-        <v>1549</v>
+        <v>2030</v>
       </c>
       <c r="D41">
-        <v>0.1672046481601033</v>
+        <v>0.07980295566502463</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B42">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="C42">
-        <v>1532</v>
+        <v>2024</v>
       </c>
       <c r="D42">
-        <v>0.1684073107049608</v>
+        <v>0.108695652173913</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B43">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="C43">
-        <v>1583</v>
+        <v>1970</v>
       </c>
       <c r="D43">
-        <v>0.1440303221730891</v>
+        <v>0.132994923857868</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B44">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="C44">
-        <v>1728</v>
+        <v>1988</v>
       </c>
       <c r="D44">
-        <v>0.1203703703703704</v>
+        <v>0.1413480885311871</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B45">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C45">
-        <v>1757</v>
+        <v>1980</v>
       </c>
       <c r="D45">
-        <v>0.1394422310756972</v>
+        <v>0.143939393939394</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B46">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="C46">
-        <v>1753</v>
+        <v>1985</v>
       </c>
       <c r="D46">
-        <v>0.1175128351397604</v>
+        <v>0.1561712846347607</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B47">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C47">
-        <v>1742</v>
+        <v>1533</v>
       </c>
       <c r="D47">
-        <v>0.1521239954075775</v>
+        <v>0.09915198956294846</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B48">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="C48">
-        <v>1750</v>
+        <v>1507</v>
       </c>
       <c r="D48">
-        <v>0.144</v>
+        <v>0.1088254810882548</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B49">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C49">
-        <v>1754</v>
+        <v>1565</v>
       </c>
       <c r="D49">
-        <v>0.1510832383124287</v>
+        <v>0.1022364217252396</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B50">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C50">
-        <v>1697</v>
+        <v>1601</v>
       </c>
       <c r="D50">
-        <v>0.1655863288155569</v>
+        <v>0.1024359775140537</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B51">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C51">
-        <v>1679</v>
+        <v>1583</v>
       </c>
       <c r="D51">
-        <v>0.1494937462775462</v>
+        <v>0.09475679090334807</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B52">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C52">
-        <v>1727</v>
+        <v>1596</v>
       </c>
       <c r="D52">
-        <v>0.06601042269832079</v>
+        <v>0.09586466165413533</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B53">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C53">
-        <v>1695</v>
+        <v>1587</v>
       </c>
       <c r="D53">
-        <v>0.01710914454277286</v>
+        <v>0.1090107120352867</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B54">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C54">
-        <v>1996</v>
+        <v>1603</v>
       </c>
       <c r="D54">
-        <v>0.09919839679358718</v>
+        <v>0.1210230817217717</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B55">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C55">
-        <v>2026</v>
+        <v>1656</v>
       </c>
       <c r="D55">
-        <v>0.09180651530108588</v>
+        <v>0.1099033816425121</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B56">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C56">
-        <v>1955</v>
+        <v>1736</v>
       </c>
       <c r="D56">
-        <v>0.09769820971867008</v>
+        <v>0.07603686635944701</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B57">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C57">
-        <v>2030</v>
+        <v>1818</v>
       </c>
       <c r="D57">
-        <v>0.07980295566502463</v>
+        <v>0.09900990099009901</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B58">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C58">
-        <v>2024</v>
+        <v>1820</v>
       </c>
       <c r="D58">
-        <v>0.108695652173913</v>
+        <v>0.1010989010989011</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B59">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C59">
-        <v>1970</v>
+        <v>1844</v>
       </c>
       <c r="D59">
-        <v>0.132994923857868</v>
+        <v>0.06073752711496746</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B60">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C60">
-        <v>1988</v>
+        <v>1836</v>
       </c>
       <c r="D60">
-        <v>0.1413480885311871</v>
+        <v>0.06100217864923747</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B61">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C61">
-        <v>1980</v>
+        <v>1787</v>
       </c>
       <c r="D61">
-        <v>0.143939393939394</v>
+        <v>0.08282036933407946</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B62">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C62">
-        <v>1985</v>
+        <v>1832</v>
       </c>
       <c r="D62">
-        <v>0.1561712846347607</v>
+        <v>0.09934497816593886</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B63">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C63">
-        <v>2004</v>
+        <v>1821</v>
       </c>
       <c r="D63">
-        <v>0.125249500998004</v>
+        <v>0.114772103239978</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B64">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C64">
-        <v>1978</v>
+        <v>1850</v>
       </c>
       <c r="D64">
-        <v>0.08796764408493428</v>
+        <v>0.1254054054054054</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B65">
-        <v>2021</v>
+        <v>2010</v>
       </c>
       <c r="C65">
-        <v>1938</v>
+        <v>1628</v>
       </c>
       <c r="D65">
-        <v>0.05159958720330237</v>
+        <v>0.105036855036855</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B66">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C66">
-        <v>1946</v>
+        <v>1992</v>
       </c>
       <c r="D66">
-        <v>0.0118191161356629</v>
+        <v>0.09839357429718876</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B67">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C67">
-        <v>1533</v>
+        <v>1814</v>
       </c>
       <c r="D67">
-        <v>0.09915198956294846</v>
+        <v>0.09371554575523705</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B68">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="C68">
-        <v>1507</v>
+        <v>1830</v>
       </c>
       <c r="D68">
-        <v>0.1088254810882548</v>
+        <v>0.08852459016393442</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B69">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C69">
-        <v>1565</v>
+        <v>1838</v>
       </c>
       <c r="D69">
-        <v>0.1022364217252396</v>
+        <v>0.07236126224156691</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B70">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="C70">
-        <v>1601</v>
+        <v>1716</v>
       </c>
       <c r="D70">
-        <v>0.1024359775140537</v>
+        <v>0.06060606060606061</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B71">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C71">
-        <v>1583</v>
+        <v>1607</v>
       </c>
       <c r="D71">
-        <v>0.09475679090334807</v>
+        <v>0.07591785936527691</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B72">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C72">
-        <v>1596</v>
+        <v>1656</v>
       </c>
       <c r="D72">
-        <v>0.09586466165413533</v>
+        <v>0.07789855072463768</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B73">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C73">
-        <v>1587</v>
+        <v>1689</v>
       </c>
       <c r="D73">
-        <v>0.1090107120352867</v>
+        <v>0.09295441089402014</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B74">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C74">
-        <v>1603</v>
+        <v>421</v>
       </c>
       <c r="D74">
-        <v>0.1210230817217717</v>
+        <v>0.07125890736342043</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B75">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C75">
-        <v>1656</v>
+        <v>414</v>
       </c>
       <c r="D75">
-        <v>0.1099033816425121</v>
+        <v>0.0748792270531401</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B76">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C76">
-        <v>1594</v>
+        <v>426</v>
       </c>
       <c r="D76">
-        <v>0.1342534504391468</v>
+        <v>0.06807511737089202</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B77">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C77">
-        <v>1592</v>
+        <v>426</v>
       </c>
       <c r="D77">
-        <v>0.09484924623115577</v>
+        <v>0.1009389671361502</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B78">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C78">
-        <v>1555</v>
+        <v>426</v>
       </c>
       <c r="D78">
-        <v>0.05916398713826367</v>
+        <v>0.04694835680751173</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B79">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C79">
-        <v>1518</v>
+        <v>416</v>
       </c>
       <c r="D79">
-        <v>0.02173913043478261</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B80">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C80">
-        <v>1736</v>
+        <v>430</v>
       </c>
       <c r="D80">
-        <v>0.07603686635944701</v>
+        <v>0.08372093023255814</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B81">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="C81">
-        <v>1818</v>
+        <v>444</v>
       </c>
       <c r="D81">
-        <v>0.09900990099009901</v>
+        <v>0.08558558558558559</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B82">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C82">
-        <v>1820</v>
+        <v>451</v>
       </c>
       <c r="D82">
-        <v>0.1010989010989011</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>2013</v>
-      </c>
-      <c r="C83">
-        <v>1844</v>
-      </c>
-      <c r="D83">
-        <v>0.06073752711496746</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>2014</v>
-      </c>
-      <c r="C84">
-        <v>1836</v>
-      </c>
-      <c r="D84">
-        <v>0.06100217864923747</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>2015</v>
-      </c>
-      <c r="C85">
-        <v>1787</v>
-      </c>
-      <c r="D85">
-        <v>0.08282036933407946</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>2016</v>
-      </c>
-      <c r="C86">
-        <v>1832</v>
-      </c>
-      <c r="D86">
-        <v>0.09934497816593886</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>2017</v>
-      </c>
-      <c r="C87">
-        <v>1821</v>
-      </c>
-      <c r="D87">
-        <v>0.114772103239978</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>2018</v>
-      </c>
-      <c r="C88">
-        <v>1850</v>
-      </c>
-      <c r="D88">
-        <v>0.1254054054054054</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>2019</v>
-      </c>
-      <c r="C89">
-        <v>1848</v>
-      </c>
-      <c r="D89">
-        <v>0.1044372294372294</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>2020</v>
-      </c>
-      <c r="C90">
-        <v>1833</v>
-      </c>
-      <c r="D90">
-        <v>0.08292416803055101</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>2021</v>
-      </c>
-      <c r="C91">
-        <v>1778</v>
-      </c>
-      <c r="D91">
-        <v>0.05230596175478065</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>2022</v>
-      </c>
-      <c r="C92">
-        <v>1782</v>
-      </c>
-      <c r="D92">
-        <v>0.01122334455667789</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>2010</v>
-      </c>
-      <c r="C93">
-        <v>1628</v>
-      </c>
-      <c r="D93">
-        <v>0.105036855036855</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>2011</v>
-      </c>
-      <c r="C94">
-        <v>1992</v>
-      </c>
-      <c r="D94">
-        <v>0.09839357429718876</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>2012</v>
-      </c>
-      <c r="C95">
-        <v>1814</v>
-      </c>
-      <c r="D95">
-        <v>0.09371554575523705</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>2013</v>
-      </c>
-      <c r="C96">
-        <v>1830</v>
-      </c>
-      <c r="D96">
-        <v>0.08852459016393442</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>2014</v>
-      </c>
-      <c r="C97">
-        <v>1838</v>
-      </c>
-      <c r="D97">
-        <v>0.07236126224156691</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>2015</v>
-      </c>
-      <c r="C98">
-        <v>1716</v>
-      </c>
-      <c r="D98">
-        <v>0.06060606060606061</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>2016</v>
-      </c>
-      <c r="C99">
-        <v>1607</v>
-      </c>
-      <c r="D99">
-        <v>0.07591785936527691</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>2017</v>
-      </c>
-      <c r="C100">
-        <v>1656</v>
-      </c>
-      <c r="D100">
-        <v>0.07789855072463768</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>2018</v>
-      </c>
-      <c r="C101">
-        <v>1689</v>
-      </c>
-      <c r="D101">
-        <v>0.09295441089402014</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B102">
-        <v>2019</v>
-      </c>
-      <c r="C102">
-        <v>1612</v>
-      </c>
-      <c r="D102">
-        <v>0.09987593052109181</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B103">
-        <v>2020</v>
-      </c>
-      <c r="C103">
-        <v>1615</v>
-      </c>
-      <c r="D103">
-        <v>0.07120743034055728</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B104">
-        <v>2021</v>
-      </c>
-      <c r="C104">
-        <v>1630</v>
-      </c>
-      <c r="D104">
-        <v>0.04662576687116565</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B105">
-        <v>2022</v>
-      </c>
-      <c r="C105">
-        <v>1540</v>
-      </c>
-      <c r="D105">
-        <v>0.01688311688311688</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B106">
-        <v>2010</v>
-      </c>
-      <c r="C106">
-        <v>421</v>
-      </c>
-      <c r="D106">
-        <v>0.07125890736342043</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B107">
-        <v>2011</v>
-      </c>
-      <c r="C107">
-        <v>414</v>
-      </c>
-      <c r="D107">
-        <v>0.0748792270531401</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B108">
-        <v>2012</v>
-      </c>
-      <c r="C108">
-        <v>426</v>
-      </c>
-      <c r="D108">
-        <v>0.06807511737089202</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B109">
-        <v>2013</v>
-      </c>
-      <c r="C109">
-        <v>426</v>
-      </c>
-      <c r="D109">
-        <v>0.1009389671361502</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B110">
-        <v>2014</v>
-      </c>
-      <c r="C110">
-        <v>426</v>
-      </c>
-      <c r="D110">
-        <v>0.04694835680751173</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B111">
-        <v>2015</v>
-      </c>
-      <c r="C111">
-        <v>416</v>
-      </c>
-      <c r="D111">
-        <v>0.07692307692307693</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B112">
-        <v>2016</v>
-      </c>
-      <c r="C112">
-        <v>430</v>
-      </c>
-      <c r="D112">
-        <v>0.08372093023255814</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B113">
-        <v>2017</v>
-      </c>
-      <c r="C113">
-        <v>444</v>
-      </c>
-      <c r="D113">
-        <v>0.08558558558558559</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B114">
-        <v>2018</v>
-      </c>
-      <c r="C114">
-        <v>451</v>
-      </c>
-      <c r="D114">
         <v>0.07317073170731707</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B115">
-        <v>2019</v>
-      </c>
-      <c r="C115">
-        <v>431</v>
-      </c>
-      <c r="D115">
-        <v>0.07192575406032482</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B116">
-        <v>2020</v>
-      </c>
-      <c r="C116">
-        <v>459</v>
-      </c>
-      <c r="D116">
-        <v>0.0915032679738562</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B117">
-        <v>2021</v>
-      </c>
-      <c r="C117">
-        <v>433</v>
-      </c>
-      <c r="D117">
-        <v>0.04387990762124711</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Linguística, Letras e Artes</t>
-        </is>
-      </c>
-      <c r="B118">
-        <v>2022</v>
-      </c>
-      <c r="C118">
-        <v>454</v>
-      </c>
-      <c r="D118">
-        <v>0.013215859030837</v>
       </c>
     </row>
   </sheetData>
